--- a/data/nzd0050/nzd0050.xlsx
+++ b/data/nzd0050/nzd0050.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E499"/>
+  <dimension ref="A1:E500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10909,6 +10909,27 @@
         <v>438.98</v>
       </c>
       <c r="E499" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>374.72</v>
+      </c>
+      <c r="C500" t="n">
+        <v>370.14</v>
+      </c>
+      <c r="D500" t="n">
+        <v>437.31</v>
+      </c>
+      <c r="E500" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -10925,7 +10946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B572"/>
+  <dimension ref="A1:B573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16648,6 +16669,16 @@
       </c>
       <c r="B572" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>
@@ -16816,28 +16847,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03163380977096967</v>
+        <v>-0.03257193824120738</v>
       </c>
       <c r="J2" t="n">
+        <v>499</v>
+      </c>
+      <c r="K2" t="n">
         <v>498</v>
       </c>
-      <c r="K2" t="n">
-        <v>497</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.00641421564788891</v>
+        <v>0.006816955698568106</v>
       </c>
       <c r="M2" t="n">
-        <v>2.31006075420034</v>
+        <v>2.310148323806852</v>
       </c>
       <c r="N2" t="n">
-        <v>8.919329001371697</v>
+        <v>8.913463631393777</v>
       </c>
       <c r="O2" t="n">
-        <v>2.986524569021942</v>
+        <v>2.985542435034843</v>
       </c>
       <c r="P2" t="n">
-        <v>378.011059760578</v>
+        <v>378.0204756351961</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16894,28 +16925,28 @@
         <v>0.0793</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07665966713601427</v>
+        <v>-0.07849699001191492</v>
       </c>
       <c r="J3" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K3" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02968046678008363</v>
+        <v>0.03107641216400669</v>
       </c>
       <c r="M3" t="n">
-        <v>2.550704252884719</v>
+        <v>2.55454066313964</v>
       </c>
       <c r="N3" t="n">
-        <v>11.03390015096013</v>
+        <v>11.05787583327669</v>
       </c>
       <c r="O3" t="n">
-        <v>3.321731498926446</v>
+        <v>3.325338453943703</v>
       </c>
       <c r="P3" t="n">
-        <v>376.9648257131682</v>
+        <v>376.9832810082408</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16972,28 +17003,28 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02872228501193123</v>
+        <v>0.02736752754671934</v>
       </c>
       <c r="J4" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K4" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004974976085601379</v>
+        <v>0.004525828301769064</v>
       </c>
       <c r="M4" t="n">
-        <v>2.363741228266551</v>
+        <v>2.366056995884674</v>
       </c>
       <c r="N4" t="n">
-        <v>9.476154309804674</v>
+        <v>9.482221491759992</v>
       </c>
       <c r="O4" t="n">
-        <v>3.078336289264815</v>
+        <v>3.079321596027279</v>
       </c>
       <c r="P4" t="n">
-        <v>440.0999889541292</v>
+        <v>440.11359704071</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17031,7 +17062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E499"/>
+  <dimension ref="A1:E500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30503,6 +30534,33 @@
         </is>
       </c>
     </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>-35.01826572014145,173.8591936306297</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>-35.01888023688355,173.85966383905682</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>-35.01876342700591,173.8607955622635</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0050/nzd0050.xlsx
+++ b/data/nzd0050/nzd0050.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E500"/>
+  <dimension ref="A1:E502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10932,6 +10932,48 @@
       <c r="E500" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>374.58</v>
+      </c>
+      <c r="C501" t="n">
+        <v>370.13</v>
+      </c>
+      <c r="D501" t="n">
+        <v>437.39</v>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>373.57</v>
+      </c>
+      <c r="C502" t="n">
+        <v>368.49</v>
+      </c>
+      <c r="D502" t="n">
+        <v>436.54</v>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -10946,7 +10988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B573"/>
+  <dimension ref="A1:B576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16679,6 +16721,36 @@
       </c>
       <c r="B573" t="n">
         <v>0.39</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -16847,28 +16919,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03257193824120738</v>
+        <v>-0.03491345134948553</v>
       </c>
       <c r="J2" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="K2" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006816955698568106</v>
+        <v>0.007855758220757236</v>
       </c>
       <c r="M2" t="n">
-        <v>2.310148323806852</v>
+        <v>2.312737471094421</v>
       </c>
       <c r="N2" t="n">
-        <v>8.913463631393777</v>
+        <v>8.916523994685226</v>
       </c>
       <c r="O2" t="n">
-        <v>2.985542435034843</v>
+        <v>2.986054921578842</v>
       </c>
       <c r="P2" t="n">
-        <v>378.0204756351961</v>
+        <v>378.0440403084046</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16925,28 +16997,28 @@
         <v>0.0793</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07849699001191492</v>
+        <v>-0.08274787053993886</v>
       </c>
       <c r="J3" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="K3" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03107641216400669</v>
+        <v>0.03431379838967152</v>
       </c>
       <c r="M3" t="n">
-        <v>2.55454066313964</v>
+        <v>2.564923527330475</v>
       </c>
       <c r="N3" t="n">
-        <v>11.05787583327669</v>
+        <v>11.14028704631074</v>
       </c>
       <c r="O3" t="n">
-        <v>3.325338453943703</v>
+        <v>3.337706854460221</v>
       </c>
       <c r="P3" t="n">
-        <v>376.9832810082408</v>
+        <v>377.0260937172659</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17003,28 +17075,28 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02736752754671934</v>
+        <v>0.02443396956310293</v>
       </c>
       <c r="J4" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="K4" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004525828301769064</v>
+        <v>0.003618416439090999</v>
       </c>
       <c r="M4" t="n">
-        <v>2.366056995884674</v>
+        <v>2.371796579146335</v>
       </c>
       <c r="N4" t="n">
-        <v>9.482221491759992</v>
+        <v>9.504093471973238</v>
       </c>
       <c r="O4" t="n">
-        <v>3.079321596027279</v>
+        <v>3.082870978807455</v>
       </c>
       <c r="P4" t="n">
-        <v>440.11359704071</v>
+        <v>440.1431417911036</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17062,7 +17134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E500"/>
+  <dimension ref="A1:E502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30561,6 +30633,60 @@
         </is>
       </c>
     </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>-35.01826645569509,173.85919238359523</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>-35.01888030201004,173.85966376325524</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>-35.018762822152915,173.8607960400292</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>-35.01827176218883,173.85918338713165</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>-35.0188909827566,173.85965133179798</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>-35.01876924871592,173.86079096376812</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0050/nzd0050.xlsx
+++ b/data/nzd0050/nzd0050.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E502"/>
+  <dimension ref="A1:E504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10974,6 +10974,48 @@
       <c r="E502" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>372.18</v>
+      </c>
+      <c r="C503" t="n">
+        <v>366.61</v>
+      </c>
+      <c r="D503" t="n">
+        <v>435.38</v>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>372.05</v>
+      </c>
+      <c r="C504" t="n">
+        <v>366.33</v>
+      </c>
+      <c r="D504" t="n">
+        <v>435.5</v>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -10988,7 +11030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B576"/>
+  <dimension ref="A1:B578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16751,6 +16793,26 @@
       </c>
       <c r="B576" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>-0.03</v>
       </c>
     </row>
   </sheetData>
@@ -16919,28 +16981,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03491345134948553</v>
+        <v>-0.03869168334805703</v>
       </c>
       <c r="J2" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K2" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007855758220757236</v>
+        <v>0.00960550751988698</v>
       </c>
       <c r="M2" t="n">
-        <v>2.312737471094421</v>
+        <v>2.322618284676254</v>
       </c>
       <c r="N2" t="n">
-        <v>8.916523994685226</v>
+        <v>8.979585079073184</v>
       </c>
       <c r="O2" t="n">
-        <v>2.986054921578842</v>
+        <v>2.996595581501312</v>
       </c>
       <c r="P2" t="n">
-        <v>378.0440403084046</v>
+        <v>378.0822236633019</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16997,28 +17059,28 @@
         <v>0.0793</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08274787053993886</v>
+        <v>-0.08907127647163932</v>
       </c>
       <c r="J3" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K3" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03431379838967152</v>
+        <v>0.03893512077078476</v>
       </c>
       <c r="M3" t="n">
-        <v>2.564923527330475</v>
+        <v>2.585589396882905</v>
       </c>
       <c r="N3" t="n">
-        <v>11.14028704631074</v>
+        <v>11.37149178803926</v>
       </c>
       <c r="O3" t="n">
-        <v>3.337706854460221</v>
+        <v>3.372164258757165</v>
       </c>
       <c r="P3" t="n">
-        <v>377.0260937172659</v>
+        <v>377.0900472490399</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17075,28 +17137,28 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02443396956310293</v>
+        <v>0.02039279926909455</v>
       </c>
       <c r="J4" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K4" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003618416439090999</v>
+        <v>0.002514660651213418</v>
       </c>
       <c r="M4" t="n">
-        <v>2.371796579146335</v>
+        <v>2.383499319665103</v>
       </c>
       <c r="N4" t="n">
-        <v>9.504093471973238</v>
+        <v>9.578813839059869</v>
       </c>
       <c r="O4" t="n">
-        <v>3.082870978807455</v>
+        <v>3.094965886574498</v>
       </c>
       <c r="P4" t="n">
-        <v>440.1431417911036</v>
+        <v>440.1840127141261</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17134,7 +17196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E502"/>
+  <dimension ref="A1:E504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30687,6 +30749,60 @@
         </is>
       </c>
     </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>-35.018279065184075,173.85917100585806</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>-35.01890322653771,173.85963708109907</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>-35.01877801908391,173.86078403616352</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>-35.018279748197955,173.8591698478971</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>-35.01890505007944,173.85963495865417</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>-35.01877711180449,173.86078475281232</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0050/nzd0050.xlsx
+++ b/data/nzd0050/nzd0050.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E504"/>
+  <dimension ref="A1:E506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11014,6 +11014,48 @@
         <v>435.5</v>
       </c>
       <c r="E504" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>371.27</v>
+      </c>
+      <c r="C505" t="n">
+        <v>366.8</v>
+      </c>
+      <c r="D505" t="n">
+        <v>435.49</v>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>370.95</v>
+      </c>
+      <c r="C506" t="n">
+        <v>366.78</v>
+      </c>
+      <c r="D506" t="n">
+        <v>435.01</v>
+      </c>
+      <c r="E506" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11030,7 +11072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B578"/>
+  <dimension ref="A1:B580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16813,6 +16855,26 @@
       </c>
       <c r="B578" t="n">
         <v>-0.03</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>0.93</v>
       </c>
     </row>
   </sheetData>
@@ -16981,28 +17043,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03869168334805703</v>
+        <v>-0.04317476695987793</v>
       </c>
       <c r="J2" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K2" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00960550751988698</v>
+        <v>0.01185098734285539</v>
       </c>
       <c r="M2" t="n">
-        <v>2.322618284676254</v>
+        <v>2.336304680916748</v>
       </c>
       <c r="N2" t="n">
-        <v>8.979585079073184</v>
+        <v>9.082461965567276</v>
       </c>
       <c r="O2" t="n">
-        <v>2.996595581501312</v>
+        <v>3.013712322961048</v>
       </c>
       <c r="P2" t="n">
-        <v>378.0822236633019</v>
+        <v>378.1278066432691</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17059,28 +17121,28 @@
         <v>0.0793</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08907127647163932</v>
+        <v>-0.09506233134015336</v>
       </c>
       <c r="J3" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K3" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03893512077078476</v>
+        <v>0.04356172500073541</v>
       </c>
       <c r="M3" t="n">
-        <v>2.585589396882905</v>
+        <v>2.605060021559823</v>
       </c>
       <c r="N3" t="n">
-        <v>11.37149178803926</v>
+        <v>11.5730509030495</v>
       </c>
       <c r="O3" t="n">
-        <v>3.372164258757165</v>
+        <v>3.401918709059566</v>
       </c>
       <c r="P3" t="n">
-        <v>377.0900472490399</v>
+        <v>377.151006713842</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17137,28 +17199,28 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02039279926909455</v>
+        <v>0.01626005457395241</v>
       </c>
       <c r="J4" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K4" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002514660651213418</v>
+        <v>0.001594129461159888</v>
       </c>
       <c r="M4" t="n">
-        <v>2.383499319665103</v>
+        <v>2.395829867053209</v>
       </c>
       <c r="N4" t="n">
-        <v>9.578813839059869</v>
+        <v>9.658431383956968</v>
       </c>
       <c r="O4" t="n">
-        <v>3.094965886574498</v>
+        <v>3.107801696369472</v>
       </c>
       <c r="P4" t="n">
-        <v>440.1840127141261</v>
+        <v>440.2260647363424</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17196,7 +17258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E504"/>
+  <dimension ref="A1:E506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30803,6 +30865,60 @@
         </is>
       </c>
     </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>-35.01828384628101,173.859162900131</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>-35.01890198913436,173.85963852132946</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>-35.018777187411104,173.86078469309157</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>-35.01828552754575,173.8591600497652</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>-35.01890211938734,173.85963836972627</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>-35.01878081652881,173.8607818264962</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0050/nzd0050.xlsx
+++ b/data/nzd0050/nzd0050.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E506"/>
+  <dimension ref="A1:E510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11058,6 +11058,90 @@
       <c r="E506" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>370.61</v>
+      </c>
+      <c r="C507" t="n">
+        <v>366.08</v>
+      </c>
+      <c r="D507" t="n">
+        <v>434.38</v>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>370.13</v>
+      </c>
+      <c r="C508" t="n">
+        <v>364.94</v>
+      </c>
+      <c r="D508" t="n">
+        <v>433.45</v>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>370.5</v>
+      </c>
+      <c r="C509" t="n">
+        <v>365.58</v>
+      </c>
+      <c r="D509" t="n">
+        <v>433.78</v>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>370.61</v>
+      </c>
+      <c r="C510" t="n">
+        <v>365.52</v>
+      </c>
+      <c r="D510" t="n">
+        <v>433.5</v>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11072,7 +11156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B580"/>
+  <dimension ref="A1:B584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16875,6 +16959,46 @@
       </c>
       <c r="B580" t="n">
         <v>0.93</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -17043,28 +17167,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04317476695987793</v>
+        <v>-0.05286255673168632</v>
       </c>
       <c r="J2" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="K2" t="n">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01185098734285539</v>
+        <v>0.01733927847399597</v>
       </c>
       <c r="M2" t="n">
-        <v>2.336304680916748</v>
+        <v>2.369818539013628</v>
       </c>
       <c r="N2" t="n">
-        <v>9.082461965567276</v>
+        <v>9.337282160525637</v>
       </c>
       <c r="O2" t="n">
-        <v>3.013712322961048</v>
+        <v>3.055696673514182</v>
       </c>
       <c r="P2" t="n">
-        <v>378.1278066432691</v>
+        <v>378.2268279503442</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17121,28 +17245,28 @@
         <v>0.0793</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09506233134015336</v>
+        <v>-0.1085785172533292</v>
       </c>
       <c r="J3" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="K3" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04356172500073541</v>
+        <v>0.0541623274528944</v>
       </c>
       <c r="M3" t="n">
-        <v>2.605060021559823</v>
+        <v>2.652987779435713</v>
       </c>
       <c r="N3" t="n">
-        <v>11.5730509030495</v>
+        <v>12.11638945182533</v>
       </c>
       <c r="O3" t="n">
-        <v>3.401918709059566</v>
+        <v>3.480860447048305</v>
       </c>
       <c r="P3" t="n">
-        <v>377.151006713842</v>
+        <v>377.2892613631215</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17199,28 +17323,28 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01626005457395241</v>
+        <v>0.006024094072613442</v>
       </c>
       <c r="J4" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="K4" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001594129461159888</v>
+        <v>0.0002146743552852159</v>
       </c>
       <c r="M4" t="n">
-        <v>2.395829867053209</v>
+        <v>2.431258360768413</v>
       </c>
       <c r="N4" t="n">
-        <v>9.658431383956968</v>
+        <v>9.946635488849797</v>
       </c>
       <c r="O4" t="n">
-        <v>3.107801696369472</v>
+        <v>3.153828703155864</v>
       </c>
       <c r="P4" t="n">
-        <v>440.2260647363424</v>
+        <v>440.3307691571033</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17258,7 +17382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E506"/>
+  <dimension ref="A1:E510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30919,6 +31043,114 @@
         </is>
       </c>
     </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>-35.01828731388945,173.8591570212514</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>-35.018906678241656,173.859633063614</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>-35.01878557974569,173.86077806408937</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>-35.01828983578633,173.85915274570232</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>-35.01891410266103,173.85962442222998</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>-35.018792611160855,173.86077251005946</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>-35.018287891824166,173.8591560414381</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>-35.01890993456601,173.8596292735335</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>-35.018790116142604,173.86077448084438</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>-35.01828731388945,173.8591570212514</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>-35.01891032532493,173.85962881872382</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>-35.01879223312778,173.86077280866326</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0050/nzd0050.xlsx
+++ b/data/nzd0050/nzd0050.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E510"/>
+  <dimension ref="A1:E513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11140,6 +11140,69 @@
         <v>433.5</v>
       </c>
       <c r="E510" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>370.52</v>
+      </c>
+      <c r="C511" t="n">
+        <v>365.06</v>
+      </c>
+      <c r="D511" t="n">
+        <v>433.38</v>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>371.07</v>
+      </c>
+      <c r="C512" t="n">
+        <v>365.38</v>
+      </c>
+      <c r="D512" t="n">
+        <v>433.06</v>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>372.02</v>
+      </c>
+      <c r="C513" t="n">
+        <v>366.45</v>
+      </c>
+      <c r="D513" t="n">
+        <v>433.81</v>
+      </c>
+      <c r="E513" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11156,7 +11219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B584"/>
+  <dimension ref="A1:B587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16999,6 +17062,36 @@
       </c>
       <c r="B584" t="n">
         <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -17167,28 +17260,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05286255673168632</v>
+        <v>-0.05904416069882475</v>
       </c>
       <c r="J2" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="K2" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01733927847399597</v>
+        <v>0.02138871718870961</v>
       </c>
       <c r="M2" t="n">
-        <v>2.369818539013628</v>
+        <v>2.390020462383454</v>
       </c>
       <c r="N2" t="n">
-        <v>9.337282160525637</v>
+        <v>9.466107605307537</v>
       </c>
       <c r="O2" t="n">
-        <v>3.055696673514182</v>
+        <v>3.076704016526052</v>
       </c>
       <c r="P2" t="n">
-        <v>378.2268279503442</v>
+        <v>378.2902164659736</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17245,28 +17338,28 @@
         <v>0.0793</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1085785172533292</v>
+        <v>-0.11822919828208</v>
       </c>
       <c r="J3" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="K3" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0541623274528944</v>
+        <v>0.06218325354669496</v>
       </c>
       <c r="M3" t="n">
-        <v>2.652987779435713</v>
+        <v>2.688950937280128</v>
       </c>
       <c r="N3" t="n">
-        <v>12.11638945182533</v>
+        <v>12.48846159322657</v>
       </c>
       <c r="O3" t="n">
-        <v>3.480860447048305</v>
+        <v>3.533901752061957</v>
       </c>
       <c r="P3" t="n">
-        <v>377.2892613631215</v>
+        <v>377.3882967993477</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17323,28 +17416,28 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006024094072613442</v>
+        <v>-0.001775902513757318</v>
       </c>
       <c r="J4" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="K4" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002146743552852159</v>
+        <v>1.835810918626724e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>2.431258360768413</v>
+        <v>2.45919373888907</v>
       </c>
       <c r="N4" t="n">
-        <v>9.946635488849797</v>
+        <v>10.17694045887092</v>
       </c>
       <c r="O4" t="n">
-        <v>3.153828703155864</v>
+        <v>3.190131730645447</v>
       </c>
       <c r="P4" t="n">
-        <v>440.3307691571033</v>
+        <v>440.4108157093922</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17382,7 +17475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E510"/>
+  <dimension ref="A1:E513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31151,6 +31244,87 @@
         </is>
       </c>
     </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>-35.01828778674513,173.85915621958597</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>-35.01891332114322,173.85962533184943</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>-35.01879314040715,173.86077209201414</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-35.01828489707148,173.85916111865237</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-35.01891123709572,173.8596277575012</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>-35.01879555981875,173.86077018094986</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>-35.01827990581654,173.85916958067534</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>-35.018904268561556,173.85963586827341</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>-35.01878988932275,173.86077466000665</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0050/nzd0050.xlsx
+++ b/data/nzd0050/nzd0050.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E513"/>
+  <dimension ref="A1:E517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11203,6 +11203,90 @@
         <v>433.81</v>
       </c>
       <c r="E513" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>372.59</v>
+      </c>
+      <c r="C514" t="n">
+        <v>366.55</v>
+      </c>
+      <c r="D514" t="n">
+        <v>434.06</v>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>373.47</v>
+      </c>
+      <c r="C515" t="n">
+        <v>367.7</v>
+      </c>
+      <c r="D515" t="n">
+        <v>434.45</v>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>374.6</v>
+      </c>
+      <c r="C516" t="n">
+        <v>369.11</v>
+      </c>
+      <c r="D516" t="n">
+        <v>435.82</v>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>375.74</v>
+      </c>
+      <c r="C517" t="n">
+        <v>371.36</v>
+      </c>
+      <c r="D517" t="n">
+        <v>437.48</v>
+      </c>
+      <c r="E517" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11219,7 +11303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B587"/>
+  <dimension ref="A1:B592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17092,6 +17176,56 @@
       </c>
       <c r="B587" t="n">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -17260,28 +17394,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05904416069882475</v>
+        <v>-0.06280992485312313</v>
       </c>
       <c r="J2" t="n">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="K2" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02138871718870961</v>
+        <v>0.02436658267990355</v>
       </c>
       <c r="M2" t="n">
-        <v>2.390020462383454</v>
+        <v>2.392756662367463</v>
       </c>
       <c r="N2" t="n">
-        <v>9.466107605307537</v>
+        <v>9.455023695731761</v>
       </c>
       <c r="O2" t="n">
-        <v>3.076704016526052</v>
+        <v>3.074902225393803</v>
       </c>
       <c r="P2" t="n">
-        <v>378.2902164659736</v>
+        <v>378.328980314225</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17338,28 +17472,28 @@
         <v>0.0793</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.11822919828208</v>
+        <v>-0.1262360935464619</v>
       </c>
       <c r="J3" t="n">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="K3" t="n">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06218325354669496</v>
+        <v>0.07000772643256159</v>
       </c>
       <c r="M3" t="n">
-        <v>2.688950937280128</v>
+        <v>2.712582531167317</v>
       </c>
       <c r="N3" t="n">
-        <v>12.48846159322657</v>
+        <v>12.648772561989</v>
       </c>
       <c r="O3" t="n">
-        <v>3.533901752061957</v>
+        <v>3.556511290856391</v>
       </c>
       <c r="P3" t="n">
-        <v>377.3882967993477</v>
+        <v>377.4707823221131</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17416,28 +17550,28 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.001775902513757318</v>
+        <v>-0.008874690297708035</v>
       </c>
       <c r="J4" t="n">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="K4" t="n">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="L4" t="n">
-        <v>1.835810918626724e-05</v>
+        <v>0.0004569306690581643</v>
       </c>
       <c r="M4" t="n">
-        <v>2.45919373888907</v>
+        <v>2.480731071353565</v>
       </c>
       <c r="N4" t="n">
-        <v>10.17694045887092</v>
+        <v>10.29450668165298</v>
       </c>
       <c r="O4" t="n">
-        <v>3.190131730645447</v>
+        <v>3.20850536568867</v>
       </c>
       <c r="P4" t="n">
-        <v>440.4108157093922</v>
+        <v>440.4839492108271</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17475,7 +17609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E513"/>
+  <dimension ref="A1:E517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31325,6 +31459,114 @@
         </is>
       </c>
     </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>-35.0182769110633,173.85917465788862</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>-35.01890361729665,173.85963662628944</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-35.01878799915738,173.86077615302543</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>-35.01827228758421,173.8591824963926</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>-35.01889612774992,173.8596453434729</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>-35.01878505049936,173.8607784821346</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>-35.01826635061601,173.85919256174301</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>-35.01888694491353,173.85965603149563</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>-35.018774692392654,173.86078666387576</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>-35.01826036110743,173.85920271616584</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>-35.01887229144932,173.85967308684613</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>-35.01876214169329,173.8607965775156</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
